--- a/output/2026-09-30_23_Malesia_Kedah_Cleaning.xlsx
+++ b/output/2026-09-30_23_Malesia_Kedah_Cleaning.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-30_23_Malesia_Kedah_Cleaning.xlsx
+++ b/output/2026-09-30_23_Malesia_Kedah_Cleaning.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Filiale nord (sede principale Johor Bahru); distributore attrezzature pulizia industriale: aspiratori, lavapavimenti, steam cleaner, prodotti chimici. Confermato via sito ufficiale e directory NEWPAGES/KICCI.</t>
+          <t>Filiale nord (sede principale Johor Bahru); distributore attrezzature pulizia industriale: aspiratori, lavapavimenti, steam cleaner, prodotti chimici. Confermato via sito ufficiale e directory NEWPAGES/KICCI. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
